--- a/Siscon Chamados.xlsx
+++ b/Siscon Chamados.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A655E229-BD7D-4A18-8DF2-F5220BFF2DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFC3B9DB-45AF-4593-B56D-D73E68F29B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="79">
   <si>
     <t>Chamados Abertos no SISCON</t>
   </si>
@@ -1452,7 +1452,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>13</c:v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M12" s="31">
         <f ca="1">COUNTIFS($A$5:$A$40,L12,$I$5:$I$40,"Dentro do prazo")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" s="31">
         <f ca="1">COUNTIFS($A$5:$A$40,L12,$I$5:$I$40,"Fora do prazo")</f>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="P12" s="3">
         <f>COUNTIFS($A$5:$A$40,L12,$H$5:$H$40,"Resolvido")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="3">
         <f t="shared" ca="1" si="0"/>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="M16" s="3">
         <f ca="1">COUNTIF($I$5:$I$40,"Dentro do prazo")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="28.5">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="M19" s="29">
         <f ca="1">COUNTIF($I$5:$I$40,"Resolvido dentro")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30" customHeight="1">
@@ -3280,11 +3280,10 @@
         <v>46286</v>
       </c>
       <c r="H29" s="59" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="58" t="str">
-        <f ca="1">IF(G29="","",IF(H29="Concluído","Concluído",IF(TODAY()&gt;G29,"Fora do prazo","Dentro do prazo")))</f>
-        <v>Dentro do prazo</v>
+        <v>20</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>53</v>
       </c>
       <c r="J29" s="60"/>
     </row>

--- a/Siscon Chamados.xlsx
+++ b/Siscon Chamados.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFC3B9DB-45AF-4593-B56D-D73E68F29B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50131F7A-175C-49C5-A348-0F8161B1999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="80">
   <si>
     <t>Chamados Abertos no SISCON</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
+  </si>
+  <si>
+    <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
   </si>
   <si>
     <t>Dashboard — Chamados SISCON</t>
@@ -975,7 +978,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1452,7 +1455,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>13</c:v>
@@ -1686,7 +1689,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2635,7 +2638,7 @@
       </c>
       <c r="M11" s="3">
         <f ca="1">COUNTIFS($A$5:$A$40,L11,$I$5:$I$40,"Dentro do prazo")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="3">
         <f ca="1">COUNTIFS($A$5:$A$40,L11,$I$5:$I$40,"Fora do prazo")</f>
@@ -2651,7 +2654,7 @@
       </c>
       <c r="Q11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30.75" customHeight="1">
@@ -2743,7 +2746,7 @@
       </c>
       <c r="Q13">
         <f ca="1">SUM(Q7:Q12)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="33" customHeight="1">
@@ -2851,7 +2854,7 @@
       </c>
       <c r="M16" s="3">
         <f ca="1">COUNTIF($I$5:$I$40,"Dentro do prazo")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="28.5">
@@ -3349,17 +3352,33 @@
       <c r="J31" s="6"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="16"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="17"/>
+      <c r="A32" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="25">
+        <v>2617057</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="18">
+        <v>46285</v>
+      </c>
+      <c r="G32" s="18">
+        <v>46290</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="I32" s="56" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Dentro do prazo</v>
       </c>
       <c r="J32" s="16"/>
     </row>
@@ -3747,7 +3766,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>

--- a/Siscon Chamados.xlsx
+++ b/Siscon Chamados.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50131F7A-175C-49C5-A348-0F8161B1999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A16F02-68A9-449D-867A-33DB463972D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="81">
   <si>
     <t>Chamados Abertos no SISCON</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
+  </si>
+  <si>
+    <t>Guia não disponível para execução de eventos por outros prestadores</t>
   </si>
   <si>
     <t>Dashboard — Chamados SISCON</t>
@@ -1455,7 +1458,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>13</c:v>
@@ -2692,7 +2695,7 @@
       </c>
       <c r="M12" s="31">
         <f ca="1">COUNTIFS($A$5:$A$40,L12,$I$5:$I$40,"Dentro do prazo")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" s="31">
         <f ca="1">COUNTIFS($A$5:$A$40,L12,$I$5:$I$40,"Fora do prazo")</f>
@@ -2708,7 +2711,7 @@
       </c>
       <c r="Q12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="32.25" customHeight="1">
@@ -2746,7 +2749,7 @@
       </c>
       <c r="Q13">
         <f ca="1">SUM(Q7:Q12)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="33" customHeight="1">
@@ -2854,7 +2857,7 @@
       </c>
       <c r="M16" s="3">
         <f ca="1">COUNTIF($I$5:$I$40,"Dentro do prazo")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="28.5">
@@ -3368,7 +3371,7 @@
         <v>34</v>
       </c>
       <c r="F32" s="18">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="G32" s="18">
         <v>46290</v>
@@ -3382,18 +3385,34 @@
       </c>
       <c r="J32" s="16"/>
     </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="26"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="23"/>
+    <row r="33" spans="1:10" ht="28.5">
+      <c r="A33" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="19">
+        <v>2617170</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="24">
+        <v>46286</v>
+      </c>
+      <c r="G33" s="24">
+        <v>46290</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>16</v>
+      </c>
       <c r="I33" s="21" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Dentro do prazo</v>
       </c>
       <c r="J33" s="6"/>
     </row>
@@ -3766,7 +3785,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
